--- a/output_excel/q1_3.xlsx
+++ b/output_excel/q1_3.xlsx
@@ -465,19 +465,19 @@
         <v>100</v>
       </c>
       <c r="B2" t="n">
-        <v>28.00004959890479</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>28.00032705865803</v>
+        <v>28.0003</v>
       </c>
       <c r="D2" t="n">
-        <v>28.00388551322058</v>
+        <v>28.0039</v>
       </c>
       <c r="E2" t="n">
-        <v>28.03210750742895</v>
+        <v>28.032</v>
       </c>
       <c r="F2" t="n">
-        <v>28.18050646659245</v>
+        <v>28.1803</v>
       </c>
     </row>
     <row r="3">
@@ -485,19 +485,19 @@
         <v>300</v>
       </c>
       <c r="B3" t="n">
-        <v>28.0408607462293</v>
+        <v>28.0408</v>
       </c>
       <c r="C3" t="n">
-        <v>28.06368305291819</v>
+        <v>28.0636</v>
       </c>
       <c r="D3" t="n">
-        <v>28.15186214277084</v>
+        <v>28.1517</v>
       </c>
       <c r="E3" t="n">
-        <v>28.36836735069105</v>
+        <v>28.3681</v>
       </c>
       <c r="F3" t="n">
-        <v>28.85078923174645</v>
+        <v>28.8504</v>
       </c>
     </row>
     <row r="4">
@@ -505,19 +505,19 @@
         <v>600</v>
       </c>
       <c r="B4" t="n">
-        <v>28.45454827940394</v>
+        <v>28.4543</v>
       </c>
       <c r="C4" t="n">
-        <v>28.53738084875905</v>
+        <v>28.5372</v>
       </c>
       <c r="D4" t="n">
-        <v>28.80556243552093</v>
+        <v>28.8053</v>
       </c>
       <c r="E4" t="n">
-        <v>29.31782750358133</v>
+        <v>29.3175</v>
       </c>
       <c r="F4" t="n">
-        <v>30.16718758520973</v>
+        <v>30.1667</v>
       </c>
     </row>
     <row r="5">
@@ -525,19 +525,19 @@
         <v>900</v>
       </c>
       <c r="B5" t="n">
-        <v>29.32655395691653</v>
+        <v>29.3262</v>
       </c>
       <c r="C5" t="n">
-        <v>29.46069935334138</v>
+        <v>29.4604</v>
       </c>
       <c r="D5" t="n">
-        <v>29.87846055318825</v>
+        <v>29.8781</v>
       </c>
       <c r="E5" t="n">
-        <v>30.61962919107367</v>
+        <v>30.6192</v>
       </c>
       <c r="F5" t="n">
-        <v>31.73332905748562</v>
+        <v>31.7329</v>
       </c>
     </row>
     <row r="6">
@@ -545,19 +545,19 @@
         <v>1200</v>
       </c>
       <c r="B6" t="n">
-        <v>30.54602215695272</v>
+        <v>30.5456</v>
       </c>
       <c r="C6" t="n">
-        <v>30.71315325408949</v>
+        <v>30.7128</v>
       </c>
       <c r="D6" t="n">
-        <v>31.22602804194743</v>
+        <v>31.2256</v>
       </c>
       <c r="E6" t="n">
-        <v>32.11695146066985</v>
+        <v>32.1166</v>
       </c>
       <c r="F6" t="n">
-        <v>33.43397909679764</v>
+        <v>33.4336</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +565,19 @@
         <v>1500</v>
       </c>
       <c r="B7" t="n">
-        <v>31.99982080138249</v>
+        <v>31.9994</v>
       </c>
       <c r="C7" t="n">
-        <v>32.19097504801912</v>
+        <v>32.1906</v>
       </c>
       <c r="D7" t="n">
-        <v>32.77081446192196</v>
+        <v>32.7705</v>
       </c>
       <c r="E7" t="n">
-        <v>33.75201486156338</v>
+        <v>33.7517</v>
       </c>
       <c r="F7" t="n">
-        <v>35.12567821539231</v>
+        <v>35.1255</v>
       </c>
     </row>
     <row r="8">
@@ -585,19 +585,19 @@
         <v>1800</v>
       </c>
       <c r="B8" t="n">
-        <v>33.58011538899359</v>
+        <v>33.5798</v>
       </c>
       <c r="C8" t="n">
-        <v>33.77669415523987</v>
+        <v>33.7764</v>
       </c>
       <c r="D8" t="n">
-        <v>34.36867721917621</v>
+        <v>34.3684</v>
       </c>
       <c r="E8" t="n">
-        <v>35.36684035617214</v>
+        <v>35.3666</v>
       </c>
       <c r="F8" t="n">
-        <v>36.79076489638436</v>
+        <v>36.7905</v>
       </c>
     </row>
   </sheetData>
